--- a/Data/Margin_Pledge.xlsx
+++ b/Data/Margin_Pledge.xlsx
@@ -1,13 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D555E22-BBBD-45C9-935C-288A0BC33C63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView minimized="1" xWindow="9690" yWindow="345" windowWidth="8520" windowHeight="10605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Margin_Pledge_Request" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -18,9 +25,62 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+  <si>
+    <t>Margin_pledge_Req_No</t>
+  </si>
+  <si>
+    <t>Client_Id</t>
+  </si>
+  <si>
+    <t>ucc_Id</t>
+  </si>
+  <si>
+    <t>tm_Id</t>
+  </si>
+  <si>
+    <t>cm_Id</t>
+  </si>
+  <si>
+    <t>ceccId</t>
+  </si>
+  <si>
+    <t>WHID</t>
+  </si>
+  <si>
+    <t>CommoditySeg</t>
+  </si>
+  <si>
+    <t>Commodity</t>
+  </si>
+  <si>
+    <t>ENWR</t>
+  </si>
+  <si>
+    <t>no_of_bags</t>
+  </si>
+  <si>
+    <t>Margin1</t>
+  </si>
+  <si>
+    <t>PR269MARGin</t>
+  </si>
+  <si>
+    <t>TM23213</t>
+  </si>
+  <si>
+    <t>CM23213</t>
+  </si>
+  <si>
+    <t>Agricultural</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,16 +88,35 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +124,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,7 +427,200 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2">
+        <v>155000010000027</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="1">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1000421</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="1">
+        <v>15</v>
+      </c>
+      <c r="J2" s="2">
+        <v>110000005360</v>
+      </c>
+      <c r="K2" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{973379A1-F3B5-41AE-BEA1-20C76935976C}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/Data/Margin_Pledge.xlsx
+++ b/Data/Margin_Pledge.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D555E22-BBBD-45C9-935C-288A0BC33C63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6243AE0-68CF-46CB-9BBA-66ED6A0A5909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="9690" yWindow="345" windowWidth="8520" windowHeight="10605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="210" yWindow="15" windowWidth="8520" windowHeight="10605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin_Pledge_Request" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>Margin_pledge_Req_No</t>
   </si>
@@ -64,16 +64,10 @@
     <t>Margin1</t>
   </si>
   <si>
-    <t>PR269MARGin</t>
-  </si>
-  <si>
-    <t>TM23213</t>
-  </si>
-  <si>
-    <t>CM23213</t>
-  </si>
-  <si>
     <t>Agricultural</t>
+  </si>
+  <si>
+    <t>c10092043</t>
   </si>
 </sst>
 </file>
@@ -434,6 +428,7 @@
     <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.140625" bestFit="1" customWidth="1"/>
@@ -480,16 +475,16 @@
         <v>11</v>
       </c>
       <c r="B2" s="2">
-        <v>155000010000027</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="1" t="s">
+        <v>100673000000011</v>
+      </c>
+      <c r="C2" s="1">
+        <v>973015</v>
+      </c>
+      <c r="D2" s="2">
+        <v>400920251740</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="F2" s="1">
         <v>11</v>
@@ -498,7 +493,7 @@
         <v>1000421</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I2" s="1">
         <v>15</v>

--- a/Data/Margin_Pledge.xlsx
+++ b/Data/Margin_Pledge.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6243AE0-68CF-46CB-9BBA-66ED6A0A5909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C62D6AB3-3403-4822-849A-7A022D89A5AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="210" yWindow="15" windowWidth="8520" windowHeight="10605" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin_Pledge_Request" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="TM_RePledge_Request" sheetId="2" r:id="rId2"/>
+    <sheet name="CM_RePledge_Request" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="51">
   <si>
     <t>Margin_pledge_Req_No</t>
   </si>
@@ -68,13 +69,124 @@
   </si>
   <si>
     <t>c10092043</t>
+  </si>
+  <si>
+    <t>TM_Client_Id</t>
+  </si>
+  <si>
+    <t>TM_pledge_Req_No</t>
+  </si>
+  <si>
+    <t>abhi121</t>
+  </si>
+  <si>
+    <t>CM_Client_Id</t>
+  </si>
+  <si>
+    <t>CM_pledge_Req_No</t>
+  </si>
+  <si>
+    <t>CC_Client_Id</t>
+  </si>
+  <si>
+    <t>abhi222</t>
+  </si>
+  <si>
+    <t>abhi223</t>
+  </si>
+  <si>
+    <t>abhi224</t>
+  </si>
+  <si>
+    <t>abhi225</t>
+  </si>
+  <si>
+    <t>abhi226</t>
+  </si>
+  <si>
+    <t>abhi227</t>
+  </si>
+  <si>
+    <t>abhi228</t>
+  </si>
+  <si>
+    <t>abhi229</t>
+  </si>
+  <si>
+    <t>abhi122</t>
+  </si>
+  <si>
+    <t>abhi123</t>
+  </si>
+  <si>
+    <t>abhi124</t>
+  </si>
+  <si>
+    <t>abhi125</t>
+  </si>
+  <si>
+    <t>abhi126</t>
+  </si>
+  <si>
+    <t>abhi127</t>
+  </si>
+  <si>
+    <t>abhi128</t>
+  </si>
+  <si>
+    <t>Margin2</t>
+  </si>
+  <si>
+    <t>Margin3</t>
+  </si>
+  <si>
+    <t>Margin4</t>
+  </si>
+  <si>
+    <t>Margin5</t>
+  </si>
+  <si>
+    <t>Margin6</t>
+  </si>
+  <si>
+    <t>Margin7</t>
+  </si>
+  <si>
+    <t>Margin8</t>
+  </si>
+  <si>
+    <t>Margin9</t>
+  </si>
+  <si>
+    <t>c10092044</t>
+  </si>
+  <si>
+    <t>c10092045</t>
+  </si>
+  <si>
+    <t>c10092046</t>
+  </si>
+  <si>
+    <t>c10092047</t>
+  </si>
+  <si>
+    <t>c10092048</t>
+  </si>
+  <si>
+    <t>c10092049</t>
+  </si>
+  <si>
+    <t>c10092050</t>
+  </si>
+  <si>
+    <t>c10092051</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -91,6 +203,35 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -137,11 +278,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -506,119 +651,485 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
+      <c r="A3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="2">
+        <v>100673000000011</v>
+      </c>
+      <c r="C3" s="1">
+        <v>973015</v>
+      </c>
+      <c r="D3" s="2">
+        <v>400920251740</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F3" s="1">
+        <v>11</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1000421</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="1">
+        <v>15</v>
+      </c>
+      <c r="J3" s="2"/>
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
+      <c r="A4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="2">
+        <v>100673000000011</v>
+      </c>
+      <c r="C4" s="1">
+        <v>973015</v>
+      </c>
+      <c r="D4" s="2">
+        <v>400920251740</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="1">
+        <v>11</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1000421</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="1">
+        <v>15</v>
+      </c>
+      <c r="J4" s="2"/>
       <c r="K4" s="1"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
+      <c r="A5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="2">
+        <v>100673000000011</v>
+      </c>
+      <c r="C5" s="1">
+        <v>973015</v>
+      </c>
+      <c r="D5" s="2">
+        <v>400920251740</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="1">
+        <v>11</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1000421</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="1">
+        <v>15</v>
+      </c>
+      <c r="J5" s="2"/>
       <c r="K5" s="1"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
+      <c r="A6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="2">
+        <v>100673000000011</v>
+      </c>
+      <c r="C6" s="1">
+        <v>973015</v>
+      </c>
+      <c r="D6" s="2">
+        <v>400920251740</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" s="1">
+        <v>11</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1000421</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I6" s="1">
+        <v>15</v>
+      </c>
+      <c r="J6" s="2"/>
       <c r="K6" s="1"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
+      <c r="A7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="2">
+        <v>100673000000011</v>
+      </c>
+      <c r="C7" s="1">
+        <v>973015</v>
+      </c>
+      <c r="D7" s="2">
+        <v>400920251740</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="1">
+        <v>11</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1000421</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="1">
+        <v>15</v>
+      </c>
+      <c r="J7" s="2"/>
       <c r="K7" s="1"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
+      <c r="A8" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" s="2">
+        <v>100673000000011</v>
+      </c>
+      <c r="C8" s="1">
+        <v>973015</v>
+      </c>
+      <c r="D8" s="2">
+        <v>400920251740</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" s="1">
+        <v>11</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1000421</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="1">
+        <v>15</v>
+      </c>
+      <c r="J8" s="2"/>
       <c r="K8" s="1"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
+      <c r="A9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="2">
+        <v>100673000000011</v>
+      </c>
+      <c r="C9" s="1">
+        <v>973015</v>
+      </c>
+      <c r="D9" s="2">
+        <v>400920251740</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="1">
+        <v>11</v>
+      </c>
+      <c r="G9" s="1">
+        <v>1000421</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I9" s="1">
+        <v>15</v>
+      </c>
+      <c r="J9" s="2"/>
       <c r="K9" s="1"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
+      <c r="A10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="2">
+        <v>100673000000011</v>
+      </c>
+      <c r="C10" s="1">
+        <v>973015</v>
+      </c>
+      <c r="D10" s="2">
+        <v>400920251740</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" s="1">
+        <v>11</v>
+      </c>
+      <c r="G10" s="1">
+        <v>1000421</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="1">
+        <v>15</v>
+      </c>
+      <c r="J10" s="2"/>
       <c r="K10" s="1"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{973379A1-F3B5-41AE-BEA1-20C76935976C}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="7">
+        <v>100673000099997</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="7">
+        <v>100673000019391</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="7">
+        <v>100673000099997</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="7">
+        <v>100673000019391</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="7">
+        <v>100673000099997</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="7">
+        <v>100673000019391</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="7">
+        <v>100673000099997</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="7">
+        <v>100673000019391</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="7">
+        <v>100673000099997</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="7">
+        <v>100673000019391</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="7">
+        <v>100673000099997</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="7">
+        <v>100673000019391</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="7">
+        <v>100673000099997</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="7">
+        <v>100673000019391</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="7">
+        <v>100673000099997</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="7">
+        <v>100673000019391</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{639658F1-70AF-4E5B-B314-4971BA66CF99}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="7">
+        <v>100673000019391</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="7">
+        <v>180000110000033</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="7">
+        <v>100673000019391</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="7">
+        <v>180000110000033</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="7">
+        <v>100673000019391</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="7">
+        <v>180000110000033</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="7">
+        <v>100673000019391</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" s="7">
+        <v>180000110000033</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="7">
+        <v>100673000019391</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="7">
+        <v>180000110000033</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="7">
+        <v>100673000019391</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="7">
+        <v>180000110000033</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="7">
+        <v>100673000019391</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="7">
+        <v>180000110000033</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="7">
+        <v>100673000019391</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="7">
+        <v>180000110000033</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Data/Margin_Pledge.xlsx
+++ b/Data/Margin_Pledge.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C62D6AB3-3403-4822-849A-7A022D89A5AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF0D928-7F0D-413B-B8A0-938E0CAD5E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin_Pledge_Request" sheetId="1" r:id="rId1"/>
@@ -676,10 +676,14 @@
         <v>12</v>
       </c>
       <c r="I3" s="1">
-        <v>15</v>
-      </c>
-      <c r="J3" s="2"/>
-      <c r="K3" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="J3" s="2">
+        <v>110001030649</v>
+      </c>
+      <c r="K3" s="1">
+        <v>100</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">

--- a/Data/Margin_Pledge.xlsx
+++ b/Data/Margin_Pledge.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AF0D928-7F0D-413B-B8A0-938E0CAD5E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8253FC13-064A-4834-AC5D-CED11BDC734F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin_Pledge_Request" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="53">
   <si>
     <t>Margin_pledge_Req_No</t>
   </si>
@@ -180,13 +180,20 @@
   </si>
   <si>
     <t>c10092051</t>
+  </si>
+  <si>
+    <t>Margin Pledge Sequence No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+600</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -236,6 +243,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="At"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -278,7 +291,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -287,6 +300,11 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -568,7 +586,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
@@ -580,7 +598,7 @@
     <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -615,7 +633,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
@@ -650,7 +668,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
         <v>35</v>
       </c>
@@ -685,7 +703,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
         <v>36</v>
       </c>
@@ -716,7 +734,7 @@
       <c r="J4" s="2"/>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
         <v>37</v>
       </c>
@@ -747,7 +765,7 @@
       <c r="J5" s="2"/>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
         <v>38</v>
       </c>
@@ -778,7 +796,7 @@
       <c r="J6" s="2"/>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
         <v>39</v>
       </c>
@@ -809,7 +827,7 @@
       <c r="J7" s="2"/>
       <c r="K7" s="1"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
         <v>40</v>
       </c>
@@ -840,7 +858,7 @@
       <c r="J8" s="2"/>
       <c r="K8" s="1"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
         <v>41</v>
       </c>
@@ -871,7 +889,7 @@
       <c r="J9" s="2"/>
       <c r="K9" s="1"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
         <v>42</v>
       </c>
@@ -911,14 +929,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{973379A1-F3B5-41AE-BEA1-20C76935976C}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" s="5" t="s">
         <v>14</v>
       </c>
@@ -929,7 +947,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" s="7">
         <v>100673000099997</v>
       </c>
@@ -940,7 +958,7 @@
         <v>100673000019391</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" s="7">
         <v>100673000099997</v>
       </c>
@@ -951,7 +969,7 @@
         <v>100673000019391</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" s="7">
         <v>100673000099997</v>
       </c>
@@ -962,7 +980,7 @@
         <v>100673000019391</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" s="7">
         <v>100673000099997</v>
       </c>
@@ -973,7 +991,7 @@
         <v>100673000019391</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" s="7">
         <v>100673000099997</v>
       </c>
@@ -984,7 +1002,7 @@
         <v>100673000019391</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" s="7">
         <v>100673000099997</v>
       </c>
@@ -995,7 +1013,7 @@
         <v>100673000019391</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" s="7">
         <v>100673000099997</v>
       </c>
@@ -1006,7 +1024,7 @@
         <v>100673000019391</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" s="7">
         <v>100673000099997</v>
       </c>
@@ -1025,15 +1043,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{639658F1-70AF-4E5B-B314-4971BA66CF99}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.5703125" customWidth="1"/>
+    <col min="4" max="4" width="26.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" s="5" t="s">
         <v>17</v>
       </c>
@@ -1043,8 +1062,11 @@
       <c r="C1" s="5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" s="8" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="30">
       <c r="A2" s="7">
         <v>100673000019391</v>
       </c>
@@ -1054,8 +1076,11 @@
       <c r="C2" s="7">
         <v>180000110000033</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" s="10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="7">
         <v>100673000019391</v>
       </c>
@@ -1065,8 +1090,9 @@
       <c r="C3" s="7">
         <v>180000110000033</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" s="9"/>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="7">
         <v>100673000019391</v>
       </c>
@@ -1076,8 +1102,9 @@
       <c r="C4" s="7">
         <v>180000110000033</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" s="9"/>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="7">
         <v>100673000019391</v>
       </c>
@@ -1087,8 +1114,9 @@
       <c r="C5" s="7">
         <v>180000110000033</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" s="9"/>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="7">
         <v>100673000019391</v>
       </c>
@@ -1098,8 +1126,9 @@
       <c r="C6" s="7">
         <v>180000110000033</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" s="9"/>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="7">
         <v>100673000019391</v>
       </c>
@@ -1109,8 +1138,9 @@
       <c r="C7" s="7">
         <v>180000110000033</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" s="9"/>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="7">
         <v>100673000019391</v>
       </c>
@@ -1120,8 +1150,9 @@
       <c r="C8" s="7">
         <v>180000110000033</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" s="9"/>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="7">
         <v>100673000019391</v>
       </c>
@@ -1131,6 +1162,7 @@
       <c r="C9" s="7">
         <v>180000110000033</v>
       </c>
+      <c r="D9" s="9"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>

--- a/Data/Margin_Pledge.xlsx
+++ b/Data/Margin_Pledge.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8253FC13-064A-4834-AC5D-CED11BDC734F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD687A14-9DAB-4A1C-B404-598C8B2FF387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin_Pledge_Request" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="55">
   <si>
     <t>Margin_pledge_Req_No</t>
   </si>
@@ -187,6 +187,12 @@
   <si>
     <t xml:space="preserve">
 600</t>
+  </si>
+  <si>
+    <t>Margin10</t>
+  </si>
+  <si>
+    <t>Margin11</t>
   </si>
 </sst>
 </file>
@@ -291,7 +297,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -305,6 +311,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -585,7 +592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
@@ -731,8 +738,12 @@
       <c r="I4" s="1">
         <v>15</v>
       </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="1"/>
+      <c r="J4" s="2">
+        <v>110001023792</v>
+      </c>
+      <c r="K4" s="1">
+        <v>100</v>
+      </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
@@ -762,8 +773,12 @@
       <c r="I5" s="1">
         <v>15</v>
       </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="1"/>
+      <c r="J5" s="2">
+        <v>110001031621</v>
+      </c>
+      <c r="K5" s="1">
+        <v>100</v>
+      </c>
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
@@ -793,8 +808,12 @@
       <c r="I6" s="1">
         <v>15</v>
       </c>
-      <c r="J6" s="2"/>
-      <c r="K6" s="1"/>
+      <c r="J6" s="2">
+        <v>110001031605</v>
+      </c>
+      <c r="K6" s="1">
+        <v>100</v>
+      </c>
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
@@ -824,8 +843,12 @@
       <c r="I7" s="1">
         <v>15</v>
       </c>
-      <c r="J7" s="2"/>
-      <c r="K7" s="1"/>
+      <c r="J7" s="2">
+        <v>110001031589</v>
+      </c>
+      <c r="K7" s="1">
+        <v>100</v>
+      </c>
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
@@ -855,8 +878,12 @@
       <c r="I8" s="1">
         <v>15</v>
       </c>
-      <c r="J8" s="2"/>
-      <c r="K8" s="1"/>
+      <c r="J8" s="2">
+        <v>110001031522</v>
+      </c>
+      <c r="K8" s="1">
+        <v>100</v>
+      </c>
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
@@ -886,8 +913,12 @@
       <c r="I9" s="1">
         <v>15</v>
       </c>
-      <c r="J9" s="2"/>
-      <c r="K9" s="1"/>
+      <c r="J9" s="2">
+        <v>110001031548</v>
+      </c>
+      <c r="K9" s="1">
+        <v>100</v>
+      </c>
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
@@ -917,8 +948,80 @@
       <c r="I10" s="1">
         <v>15</v>
       </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="1"/>
+      <c r="J10" s="2">
+        <v>110001031563</v>
+      </c>
+      <c r="K10" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="2">
+        <v>100673000000011</v>
+      </c>
+      <c r="C11" s="1">
+        <v>973015</v>
+      </c>
+      <c r="D11" s="2">
+        <v>400920251740</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="1">
+        <v>11</v>
+      </c>
+      <c r="G11" s="1">
+        <v>1000421</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="1">
+        <v>15</v>
+      </c>
+      <c r="J11" s="11">
+        <v>110001031647</v>
+      </c>
+      <c r="K11" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="2">
+        <v>100673000000011</v>
+      </c>
+      <c r="C12" s="1">
+        <v>973015</v>
+      </c>
+      <c r="D12" s="2">
+        <v>400920251740</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="1">
+        <v>11</v>
+      </c>
+      <c r="G12" s="1">
+        <v>1000421</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I12" s="1">
+        <v>15</v>
+      </c>
+      <c r="J12" s="9"/>
+      <c r="K12" s="1">
+        <v>100</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>

--- a/Data/Margin_Pledge.xlsx
+++ b/Data/Margin_Pledge.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD687A14-9DAB-4A1C-B404-598C8B2FF387}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{163E99E1-F4F7-47A9-BADB-0084E70C48F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin_Pledge_Request" sheetId="1" r:id="rId1"/>
@@ -77,9 +77,6 @@
     <t>TM_pledge_Req_No</t>
   </si>
   <si>
-    <t>abhi121</t>
-  </si>
-  <si>
     <t>CM_Client_Id</t>
   </si>
   <si>
@@ -89,9 +86,6 @@
     <t>CC_Client_Id</t>
   </si>
   <si>
-    <t>abhi222</t>
-  </si>
-  <si>
     <t>abhi223</t>
   </si>
   <si>
@@ -185,21 +179,27 @@
     <t>Margin Pledge Sequence No</t>
   </si>
   <si>
+    <t>Margin10</t>
+  </si>
+  <si>
+    <t>Margin11</t>
+  </si>
+  <si>
+    <t>abhu</t>
+  </si>
+  <si>
     <t xml:space="preserve">
-600</t>
-  </si>
-  <si>
-    <t>Margin10</t>
-  </si>
-  <si>
-    <t>Margin11</t>
+601</t>
+  </si>
+  <si>
+    <t>abh8</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -254,6 +254,12 @@
       <sz val="9"/>
       <color rgb="FF1F1F1F"/>
       <name val="At"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF2A314A"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -311,7 +317,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -677,7 +683,7 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2">
         <v>100673000000011</v>
@@ -689,7 +695,7 @@
         <v>400920251740</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F3" s="1">
         <v>11</v>
@@ -712,7 +718,7 @@
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2">
         <v>100673000000011</v>
@@ -724,7 +730,7 @@
         <v>400920251740</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F4" s="1">
         <v>11</v>
@@ -747,7 +753,7 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B5" s="2">
         <v>100673000000011</v>
@@ -759,7 +765,7 @@
         <v>400920251740</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F5" s="1">
         <v>11</v>
@@ -782,7 +788,7 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B6" s="2">
         <v>100673000000011</v>
@@ -794,7 +800,7 @@
         <v>400920251740</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F6" s="1">
         <v>11</v>
@@ -817,7 +823,7 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B7" s="2">
         <v>100673000000011</v>
@@ -829,7 +835,7 @@
         <v>400920251740</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F7" s="1">
         <v>11</v>
@@ -852,7 +858,7 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B8" s="2">
         <v>100673000000011</v>
@@ -864,7 +870,7 @@
         <v>400920251740</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F8" s="1">
         <v>11</v>
@@ -887,7 +893,7 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B9" s="2">
         <v>100673000000011</v>
@@ -899,7 +905,7 @@
         <v>400920251740</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F9" s="1">
         <v>11</v>
@@ -922,7 +928,7 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B10" s="2">
         <v>100673000000011</v>
@@ -934,7 +940,7 @@
         <v>400920251740</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F10" s="1">
         <v>11</v>
@@ -957,7 +963,7 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B11" s="2">
         <v>100673000000011</v>
@@ -969,7 +975,7 @@
         <v>400920251740</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F11" s="1">
         <v>11</v>
@@ -983,7 +989,7 @@
       <c r="I11" s="1">
         <v>15</v>
       </c>
-      <c r="J11" s="11">
+      <c r="J11" s="2">
         <v>110001031647</v>
       </c>
       <c r="K11" s="1">
@@ -992,7 +998,7 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B12" s="2">
         <v>100673000000011</v>
@@ -1004,7 +1010,7 @@
         <v>400920251740</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F12" s="1">
         <v>11</v>
@@ -1047,15 +1053,15 @@
         <v>15</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="7">
         <v>100673000099997</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>16</v>
+      <c r="B2" s="11" t="s">
+        <v>52</v>
       </c>
       <c r="C2" s="7">
         <v>100673000019391</v>
@@ -1066,7 +1072,7 @@
         <v>100673000099997</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C3" s="7">
         <v>100673000019391</v>
@@ -1077,7 +1083,7 @@
         <v>100673000099997</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C4" s="7">
         <v>100673000019391</v>
@@ -1088,7 +1094,7 @@
         <v>100673000099997</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C5" s="7">
         <v>100673000019391</v>
@@ -1099,7 +1105,7 @@
         <v>100673000099997</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C6" s="7">
         <v>100673000019391</v>
@@ -1110,7 +1116,7 @@
         <v>100673000099997</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C7" s="7">
         <v>100673000019391</v>
@@ -1121,7 +1127,7 @@
         <v>100673000099997</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C8" s="7">
         <v>100673000019391</v>
@@ -1132,7 +1138,7 @@
         <v>100673000099997</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C9" s="7">
         <v>100673000019391</v>
@@ -1157,16 +1163,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>19</v>
-      </c>
       <c r="D1" s="8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="30">
@@ -1174,13 +1180,13 @@
         <v>100673000019391</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="C2" s="7">
         <v>180000110000033</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1188,7 +1194,7 @@
         <v>100673000019391</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C3" s="7">
         <v>180000110000033</v>
@@ -1200,7 +1206,7 @@
         <v>100673000019391</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C4" s="7">
         <v>180000110000033</v>
@@ -1212,7 +1218,7 @@
         <v>100673000019391</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C5" s="7">
         <v>180000110000033</v>
@@ -1224,7 +1230,7 @@
         <v>100673000019391</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C6" s="7">
         <v>180000110000033</v>
@@ -1236,7 +1242,7 @@
         <v>100673000019391</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C7" s="7">
         <v>180000110000033</v>
@@ -1248,7 +1254,7 @@
         <v>100673000019391</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C8" s="7">
         <v>180000110000033</v>
@@ -1260,7 +1266,7 @@
         <v>100673000019391</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C9" s="7">
         <v>180000110000033</v>

--- a/Data/Margin_Pledge.xlsx
+++ b/Data/Margin_Pledge.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{163E99E1-F4F7-47A9-BADB-0084E70C48F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54B2272B-89D1-461D-B4B2-B548D05A74D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Margin_Pledge_Request" sheetId="1" r:id="rId1"/>
@@ -185,14 +185,14 @@
     <t>Margin11</t>
   </si>
   <si>
-    <t>abhu</t>
-  </si>
-  <si>
     <t xml:space="preserve">
 601</t>
   </si>
   <si>
-    <t>abh8</t>
+    <t>ABHITM7</t>
+  </si>
+  <si>
+    <t>ABHICM1</t>
   </si>
 </sst>
 </file>
@@ -303,7 +303,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -318,6 +318,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -598,7 +599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
@@ -1027,6 +1028,62 @@
       <c r="J12" s="9"/>
       <c r="K12" s="1">
         <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="6:8">
+      <c r="F17" s="12">
+        <v>110001032140</v>
+      </c>
+      <c r="H17" s="12">
+        <v>110001032140</v>
+      </c>
+    </row>
+    <row r="18" spans="6:8">
+      <c r="F18" s="12">
+        <v>110001032165</v>
+      </c>
+      <c r="H18" s="12">
+        <v>110001032165</v>
+      </c>
+    </row>
+    <row r="19" spans="6:8">
+      <c r="F19" s="12">
+        <v>110001032124</v>
+      </c>
+      <c r="H19" s="12">
+        <v>110001032124</v>
+      </c>
+    </row>
+    <row r="20" spans="6:8">
+      <c r="F20" s="12">
+        <v>110001032108</v>
+      </c>
+      <c r="H20" s="12">
+        <v>110001032108</v>
+      </c>
+    </row>
+    <row r="21" spans="6:8">
+      <c r="F21" s="12">
+        <v>110001032181</v>
+      </c>
+      <c r="H21" s="12">
+        <v>110001032181</v>
+      </c>
+    </row>
+    <row r="22" spans="6:8">
+      <c r="F22" s="12">
+        <v>110001032207</v>
+      </c>
+      <c r="H22" s="12">
+        <v>110001032207</v>
+      </c>
+    </row>
+    <row r="23" spans="6:8">
+      <c r="F23" s="12">
+        <v>110001032223</v>
+      </c>
+      <c r="H23" s="12">
+        <v>110001032223</v>
       </c>
     </row>
   </sheetData>
@@ -1061,7 +1118,7 @@
         <v>100673000099997</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C2" s="7">
         <v>100673000019391</v>
@@ -1177,7 +1234,7 @@
     </row>
     <row r="2" spans="1:4" ht="30">
       <c r="A2" s="7">
-        <v>100673000019391</v>
+        <v>180000110000033</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>54</v>
@@ -1186,7 +1243,7 @@
         <v>180000110000033</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:4">
